--- a/erp-server/erp-server-plm/src/main/resources/excel/productSkuDetail.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productSkuDetail.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12540"/>
+    <workbookView windowWidth="28125" windowHeight="11940"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -279,7 +279,7 @@
     <t>单箱重量</t>
   </si>
   <si>
-    <t>{.spu}</t>
+    <t>{.spuNo}</t>
   </si>
   <si>
     <t>{.name}</t>
@@ -351,7 +351,7 @@
     <t>{.targetGpm}</t>
   </si>
   <si>
-    <t>{.actualGpmGny}</t>
+    <t>{.actualGpmCny}</t>
   </si>
   <si>
     <t>{.actualGpmUsd}</t>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productSkuDetail.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productSkuDetail.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="11940"/>
+    <workbookView windowWidth="28125" windowHeight="12540"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,10 +14,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="98">
   <si>
     <r>
       <rPr>
+        <b/>
         <sz val="10"/>
         <color rgb="FFD83931"/>
         <rFont val="微软雅黑"/>
@@ -27,6 +28,7 @@
     </r>
     <r>
       <rPr>
+        <b/>
         <sz val="10"/>
         <color rgb="FF1F2329"/>
         <rFont val="微软雅黑"/>
@@ -38,6 +40,7 @@
   <si>
     <r>
       <rPr>
+        <b/>
         <sz val="10"/>
         <color rgb="FFD83931"/>
         <rFont val="微软雅黑"/>
@@ -47,6 +50,7 @@
     </r>
     <r>
       <rPr>
+        <b/>
         <sz val="10"/>
         <color rgb="FF1F2329"/>
         <rFont val="微软雅黑"/>
@@ -58,6 +62,7 @@
   <si>
     <r>
       <rPr>
+        <b/>
         <sz val="10"/>
         <color rgb="FFD83931"/>
         <rFont val="微软雅黑"/>
@@ -67,6 +72,7 @@
     </r>
     <r>
       <rPr>
+        <b/>
         <sz val="10"/>
         <color rgb="FF1F2329"/>
         <rFont val="微软雅黑"/>
@@ -99,6 +105,7 @@
   <si>
     <r>
       <rPr>
+        <b/>
         <sz val="10"/>
         <color rgb="FFD83931"/>
         <rFont val="微软雅黑"/>
@@ -108,6 +115,7 @@
     </r>
     <r>
       <rPr>
+        <b/>
         <sz val="10"/>
         <color rgb="FF1F2329"/>
         <rFont val="微软雅黑"/>
@@ -119,6 +127,7 @@
   <si>
     <r>
       <rPr>
+        <b/>
         <sz val="10"/>
         <color rgb="FFD83931"/>
         <rFont val="微软雅黑"/>
@@ -128,6 +137,7 @@
     </r>
     <r>
       <rPr>
+        <b/>
         <sz val="10"/>
         <color rgb="FF1F2329"/>
         <rFont val="微软雅黑"/>
@@ -137,7 +147,7 @@
     </r>
   </si>
   <si>
-    <t>属性</t>
+    <t>变体属性</t>
   </si>
   <si>
     <t>品牌</t>
@@ -151,6 +161,7 @@
   <si>
     <r>
       <rPr>
+        <b/>
         <sz val="10"/>
         <color rgb="FFD83931"/>
         <rFont val="微软雅黑"/>
@@ -160,6 +171,7 @@
     </r>
     <r>
       <rPr>
+        <b/>
         <sz val="10"/>
         <color rgb="FF1F2329"/>
         <rFont val="微软雅黑"/>
@@ -171,6 +183,7 @@
   <si>
     <r>
       <rPr>
+        <b/>
         <sz val="10"/>
         <color rgb="FFD83931"/>
         <rFont val="微软雅黑"/>
@@ -180,6 +193,7 @@
     </r>
     <r>
       <rPr>
+        <b/>
         <sz val="10"/>
         <color rgb="FF1F2329"/>
         <rFont val="微软雅黑"/>
@@ -241,6 +255,9 @@
   </si>
   <si>
     <t>销售状态</t>
+  </si>
+  <si>
+    <t>属性</t>
   </si>
   <si>
     <t>报关中文名</t>
@@ -436,141 +453,12 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -578,30 +466,177 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <color rgb="FFD83931"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <color rgb="FF1F2329"/>
       <name val="微软雅黑"/>
@@ -931,10 +966,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -943,141 +978,150 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1451,302 +1495,302 @@
     <col min="34" max="35" width="11.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:49">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="1" customFormat="1" ht="16.5" spans="1:49">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AD1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AE1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AG1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AH1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AI1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AK1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AL1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AM1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AN1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AO1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AP1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AQ1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AR1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AS1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AT1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AU1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AV1" s="3" t="s">
         <v>47</v>
+      </c>
+      <c r="AW1" s="3" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:49">
-      <c r="A2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="B2" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="C2" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="D2" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="E2" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="F2" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="G2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="H2" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="I2" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="J2" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="K2" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="L2" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="M2" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="N2" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="O2" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="P2" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="Q2" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="R2" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="S2" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="T2" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="U2" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="V2" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="W2" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="X2" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="Z2" s="1" t="s">
+      <c r="Y2" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="AA2" s="1" t="s">
+      <c r="Z2" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="AB2" s="1" t="s">
+      <c r="AA2" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="AC2" s="1" t="s">
+      <c r="AB2" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="AD2" s="1" t="s">
+      <c r="AC2" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="AE2" s="1" t="s">
+      <c r="AD2" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="AF2" s="1" t="s">
+      <c r="AE2" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="AG2" s="1" t="s">
+      <c r="AF2" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="AH2" s="1" t="s">
+      <c r="AG2" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="AI2" s="1" t="s">
+      <c r="AH2" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="AJ2" s="1" t="s">
+      <c r="AI2" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="AK2" s="1" t="s">
+      <c r="AJ2" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="AL2" s="1" t="s">
+      <c r="AK2" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="AM2" s="1" t="s">
+      <c r="AL2" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="AN2" s="1" t="s">
+      <c r="AM2" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="AO2" s="1" t="s">
+      <c r="AN2" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="AP2" s="1" t="s">
+      <c r="AO2" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="AQ2" s="1" t="s">
+      <c r="AP2" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="AR2" s="1" t="s">
+      <c r="AQ2" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="AS2" s="1" t="s">
+      <c r="AR2" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="AT2" s="1" t="s">
+      <c r="AS2" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="AU2" s="1" t="s">
+      <c r="AT2" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="AV2" s="1" t="s">
+      <c r="AU2" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="AW2" s="1" t="s">
+      <c r="AV2" s="4" t="s">
         <v>96</v>
+      </c>
+      <c r="AW2" s="4" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productSkuDetail.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productSkuDetail.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="120">
   <si>
     <r>
       <rPr>
@@ -296,6 +296,39 @@
     <t>单箱重量</t>
   </si>
   <si>
+    <t>ean码</t>
+  </si>
+  <si>
+    <t>计划首批下单量</t>
+  </si>
+  <si>
+    <t>首批下单时间</t>
+  </si>
+  <si>
+    <t>MOQ(最小起订量)</t>
+  </si>
+  <si>
+    <t>交货周期(天)</t>
+  </si>
+  <si>
+    <t>实际首批到货时间</t>
+  </si>
+  <si>
+    <t>实际首批到货量</t>
+  </si>
+  <si>
+    <t>首批到货状态</t>
+  </si>
+  <si>
+    <t>采购员</t>
+  </si>
+  <si>
+    <t>一级供应商</t>
+  </si>
+  <si>
+    <t>二级供应商</t>
+  </si>
+  <si>
     <t>{.spuNo}</t>
   </si>
   <si>
@@ -441,6 +474,39 @@
   </si>
   <si>
     <t>{.boxWeight}</t>
+  </si>
+  <si>
+    <t>{.ean}</t>
+  </si>
+  <si>
+    <t>{.planOrderQty}</t>
+  </si>
+  <si>
+    <t>{.placeOrderTime}</t>
+  </si>
+  <si>
+    <t>{.moq}</t>
+  </si>
+  <si>
+    <t>{.deliveryCycle}</t>
+  </si>
+  <si>
+    <t>{.actualArrivalTime}</t>
+  </si>
+  <si>
+    <t>{.actualArrivalQty}</t>
+  </si>
+  <si>
+    <t>{.arrivalState}</t>
+  </si>
+  <si>
+    <t>{.purchaseUser}</t>
+  </si>
+  <si>
+    <t>{.mainSupplier}</t>
+  </si>
+  <si>
+    <t>{.secondSupplier}</t>
   </si>
 </sst>
 </file>
@@ -1472,7 +1538,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AW2"/>
+  <dimension ref="A1:BH2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="2" max="2" width="13.625" customWidth="1"/>
@@ -1493,9 +1559,19 @@
     <col min="28" max="29" width="11.375" customWidth="1"/>
     <col min="30" max="30" width="13.25" customWidth="1"/>
     <col min="34" max="35" width="11.375" customWidth="1"/>
+    <col min="51" max="51" width="13.875" customWidth="1"/>
+    <col min="52" max="52" width="13.125" customWidth="1"/>
+    <col min="53" max="53" width="14.375" customWidth="1"/>
+    <col min="54" max="54" width="11.75" customWidth="1"/>
+    <col min="55" max="55" width="16.375" customWidth="1"/>
+    <col min="56" max="56" width="14.125" customWidth="1"/>
+    <col min="57" max="57" width="13.25" customWidth="1"/>
+    <col min="58" max="58" width="7.875" customWidth="1"/>
+    <col min="59" max="59" width="10.625" customWidth="1"/>
+    <col min="60" max="60" width="12.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="16.5" spans="1:49">
+    <row r="1" s="1" customFormat="1" ht="16.5" spans="1:60">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1643,157 +1719,245 @@
       <c r="AW1" s="3" t="s">
         <v>48</v>
       </c>
+      <c r="AX1" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="AY1" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AZ1" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="BA1" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="BB1" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="BC1" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="BD1" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="BE1" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF1" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG1" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH1" s="3" t="s">
+        <v>59</v>
+      </c>
     </row>
-    <row r="2" spans="1:49">
+    <row r="2" spans="1:60">
       <c r="A2" s="4" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="V2" s="4" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="X2" s="4" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="Y2" s="4" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="Z2" s="4" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="AA2" s="4" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="AB2" s="4" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="AC2" s="4" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AD2" s="4" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AE2" s="4" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AF2" s="4" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AG2" s="4" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AH2" s="4" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI2" s="4" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AJ2" s="4" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AK2" s="4" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="AL2" s="4" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="AM2" s="4" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="AN2" s="4" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="AO2" s="4" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="AP2" s="4" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="AQ2" s="4" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="AR2" s="4" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="AS2" s="4" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="AT2" s="4" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="AU2" s="4" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="AV2" s="4" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="AW2" s="4" t="s">
-        <v>97</v>
+        <v>108</v>
+      </c>
+      <c r="AX2" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="AY2" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="AZ2" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="BA2" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="BB2" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="BC2" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="BD2" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="BE2" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="BF2" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="BG2" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="BH2" s="4" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="5">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY2">
+      <formula1>0</formula1>
+      <formula2>99999999999</formula2>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AZ2 BC2">
+      <formula1>32874</formula1>
+      <formula2>2958101</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA2">
+      <formula1>0</formula1>
+      <formula2>999999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BB2">
+      <formula1>0</formula1>
+      <formula2>999999999</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BD2">
+      <formula1>0</formula1>
+      <formula2>9999999999</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
